--- a/ognami.xlsx
+++ b/ognami.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="219">
   <si>
     <t>AnaUrunKodu</t>
   </si>
@@ -797,12 +797,30 @@
       <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/5c43f336-1d8c-4180-aa3f-21cc3a0c0ae7/ogn000028.png</t>
     </r>
   </si>
+  <si>
+    <t>OGN000029</t>
+  </si>
+  <si>
+    <t>OGN9990000029</t>
+  </si>
+  <si>
+    <t>SKU000029</t>
+  </si>
+  <si>
+    <t>Pratik Tırnak Koruyucu Balık Tasarımlı Kutu İçecek Açacağı ve Anahtarlık | 2’si 1 Arada</t>
+  </si>
+  <si>
+    <t>Tırnak Dostu: Tırnak kırılması, ojelerin soyulması veya parmak acıtması gibi dertleri tamamen ortadan kaldırır. Çok Amaçlı Kullanım: Sadece bir açacak değil, aynı zamanda çantanıza ve anahtarlarınıza hava katacak sevimli bir aksesuardır.Taşıması Çok Kolay: Bilye zincirli tasarımı sayesinde çantanızda kaybolmaz; her an elinizin altında olur.Harika Bir Hediye Seçeneği: Arkadaşlarınıza, sevdiklerinize veya tırnak bakımına önem veren herkese verebileceğiniz hem kullanışlı hem de sevimli bir hediye!</t>
+  </si>
+  <si>
+    <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/9f5fd2fa-708d-4005-ba44-693d7770baf3/fishacacak.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -855,6 +873,26 @@
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="&quot;Times New Roman&quot;"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -870,7 +908,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -919,6 +957,22 @@
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1154,7 +1208,7 @@
     <col customWidth="1" min="2" max="2" width="13.88"/>
     <col customWidth="1" min="5" max="5" width="5.88"/>
     <col customWidth="1" min="8" max="8" width="8.13"/>
-    <col customWidth="1" min="13" max="13" width="17.0"/>
+    <col customWidth="1" min="13" max="13" width="787.38"/>
     <col customWidth="1" min="14" max="14" width="99.13"/>
     <col customWidth="1" min="16" max="16" width="6.38"/>
   </cols>
@@ -2591,33 +2645,120 @@
       </c>
     </row>
     <row r="30" ht="18.0" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" ht="18.0" customHeight="1"/>
-    <row r="32" ht="18.0" customHeight="1"/>
-    <row r="33" ht="18.0" customHeight="1"/>
-    <row r="34" ht="18.0" customHeight="1"/>
-    <row r="35" ht="18.0" customHeight="1"/>
-    <row r="36" ht="18.0" customHeight="1"/>
-    <row r="37" ht="18.0" customHeight="1"/>
-    <row r="38" ht="18.0" customHeight="1"/>
-    <row r="39" ht="18.0" customHeight="1"/>
-    <row r="40" ht="18.0" customHeight="1"/>
-    <row r="41" ht="18.0" customHeight="1"/>
-    <row r="42" ht="18.0" customHeight="1"/>
-    <row r="43" ht="18.0" customHeight="1"/>
-    <row r="44" ht="18.0" customHeight="1"/>
-    <row r="45" ht="18.0" customHeight="1"/>
-    <row r="46" ht="18.0" customHeight="1"/>
-    <row r="47" ht="18.0" customHeight="1"/>
-    <row r="48" ht="18.0" customHeight="1"/>
-    <row r="49" ht="18.0" customHeight="1"/>
-    <row r="50" ht="18.0" customHeight="1"/>
-    <row r="51" ht="18.0" customHeight="1"/>
-    <row r="52" ht="18.0" customHeight="1"/>
-    <row r="53" ht="18.0" customHeight="1"/>
+      <c r="A30" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="E30" s="17">
+        <v>59.0</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="16">
+        <v>129.9</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R30" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="31" ht="18.0" customHeight="1">
+      <c r="M31" s="20"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" ht="18.0" customHeight="1">
+      <c r="M32" s="20"/>
+    </row>
+    <row r="33" ht="18.0" customHeight="1">
+      <c r="M33" s="20"/>
+    </row>
+    <row r="34" ht="18.0" customHeight="1">
+      <c r="M34" s="20"/>
+    </row>
+    <row r="35" ht="18.0" customHeight="1">
+      <c r="M35" s="21"/>
+    </row>
+    <row r="36" ht="18.0" customHeight="1">
+      <c r="M36" s="20"/>
+    </row>
+    <row r="37" ht="18.0" customHeight="1">
+      <c r="M37" s="21"/>
+    </row>
+    <row r="38" ht="18.0" customHeight="1">
+      <c r="M38" s="20"/>
+    </row>
+    <row r="39" ht="18.0" customHeight="1">
+      <c r="M39" s="21"/>
+    </row>
+    <row r="40" ht="18.0" customHeight="1">
+      <c r="M40" s="20"/>
+    </row>
+    <row r="41" ht="18.0" customHeight="1">
+      <c r="M41" s="21"/>
+    </row>
+    <row r="42" ht="18.0" customHeight="1">
+      <c r="M42" s="20"/>
+    </row>
+    <row r="43" ht="18.0" customHeight="1">
+      <c r="M43" s="21"/>
+    </row>
+    <row r="44" ht="18.0" customHeight="1">
+      <c r="M44" s="20"/>
+    </row>
+    <row r="45" ht="18.0" customHeight="1">
+      <c r="M45" s="20"/>
+    </row>
+    <row r="46" ht="18.0" customHeight="1">
+      <c r="M46" s="20"/>
+    </row>
+    <row r="47" ht="18.0" customHeight="1">
+      <c r="M47" s="20"/>
+    </row>
+    <row r="48" ht="18.0" customHeight="1">
+      <c r="M48" s="21"/>
+    </row>
+    <row r="49" ht="18.0" customHeight="1">
+      <c r="M49" s="20"/>
+    </row>
+    <row r="50" ht="18.0" customHeight="1">
+      <c r="M50" s="21"/>
+    </row>
+    <row r="51" ht="18.0" customHeight="1">
+      <c r="M51" s="20"/>
+    </row>
+    <row r="52" ht="18.0" customHeight="1">
+      <c r="M52" s="20"/>
+    </row>
+    <row r="53" ht="18.0" customHeight="1">
+      <c r="M53" s="20"/>
+    </row>
     <row r="54" ht="18.0" customHeight="1"/>
     <row r="55" ht="18.0" customHeight="1"/>
     <row r="56" ht="18.0" customHeight="1"/>
@@ -3595,7 +3736,8 @@
     <hyperlink r:id="rId26" ref="N27"/>
     <hyperlink r:id="rId27" ref="N28"/>
     <hyperlink r:id="rId28" ref="N29"/>
+    <hyperlink r:id="rId29" ref="N30"/>
   </hyperlinks>
-  <drawing r:id="rId29"/>
+  <drawing r:id="rId30"/>
 </worksheet>
 </file>
--- a/ognami.xlsx
+++ b/ognami.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="248">
   <si>
     <t>AnaUrunKodu</t>
   </si>
@@ -814,6 +814,93 @@
   </si>
   <si>
     <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/9f5fd2fa-708d-4005-ba44-693d7770baf3/fishacacak.jpg</t>
+  </si>
+  <si>
+    <t>OGN000030</t>
+  </si>
+  <si>
+    <t>OGN9990000030</t>
+  </si>
+  <si>
+    <t>SKU000030</t>
+  </si>
+  <si>
+    <t>3D Baskı Sevimli Figürlü Kapı Tutucu | Pratik Doorstop Kapı Sabitleyici | Ev Ofis İçin Kapı Stoperi+</t>
+  </si>
+  <si>
+    <t>Kapı Stoperi</t>
+  </si>
+  <si>
+    <t>3D Baskı Sevimli Figürlü Kapı Tutucu, kapıların istenilen konumda açık kalmasına yardımcı olan pratik ve dekoratif bir kapı stoperidir. Figürlü tasarımı sayesinde klasik kapı stoperlerine göre daha eğlenceli bir görünüm sunar. Kapı altına yerleştirilerek kapının kapanmasını önlemeye yardımcı olur. Ev, ofis, çocuk odası, çalışma odası ve benzeri alanlarda kullanılabilir. 3D baskı teknolojisiyle üretilmiştir. Hafif ve kompakt yapıdadır. Pratik şekilde yerleştirilip çıkarılabilir. Kolay temizlenebilir. Renk: Açık mavi. Paket İçeriği: 1 adet 3D Baskı Figürlü Kapı Tutucu. Not: Ürün 3D baskı yöntemiyle üretildiğinden yüzeyinde ince katman çizgileri ve küçük dokusal farklılıklar görülebilir. Bu durum 3D baskı üretim tekniğinin doğal bir özelliğidir. Ürünün tutuş performansı kapı ağırlığına, kapı altı boşluğuna ve zemin türüne göre değişiklik gösterebilir.</t>
+  </si>
+  <si>
+    <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/526c3c49-3ee7-4d72-8fb7-616a03051a3e/52.png</t>
+  </si>
+  <si>
+    <t>OGN000031</t>
+  </si>
+  <si>
+    <t>OGN9990000031</t>
+  </si>
+  <si>
+    <t>SKU000031</t>
+  </si>
+  <si>
+    <t>3D Baskı Sevimli Hayvan Figürlü Poşet Klipsi | Paket Kapatma Mandalı | Tekrar Kullanılabilir Gıda Poşeti Klipsi</t>
+  </si>
+  <si>
+    <t>Pratik Gereçler</t>
+  </si>
+  <si>
+    <t>Renkli</t>
+  </si>
+  <si>
+    <t>3D Baskı Sevimli Hayvan Figürlü Poşet Klipsi, açılmış paketlerin ağzını pratik şekilde kapatmaya yardımcı olan, eğlenceli ve kullanışlı bir mutfak aksesuarıdır. 🐰🐶🐼🐘</t>
+  </si>
+  <si>
+    <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/e176c212-b1f1-49fb-b6dc-81ca1979d68f/ogn000031.jpg</t>
+  </si>
+  <si>
+    <t>Sevimli hayvan figürlü tasarımıyla mutfağınıza renk katarken; atıştırmalık, bakliyat, un, şeker, kahve ve benzeri paketlerin ağzını kapalı tutmaya yardımcı olur.</t>
+  </si>
+  <si>
+    <t>Ürün Özellikleri</t>
+  </si>
+  <si>
+    <t>🖨️ 3D baskı teknolojisiyle üretilmiştir.</t>
+  </si>
+  <si>
+    <t>🐾 Sevimli hayvan figürlü tasarıma sahiptir.</t>
+  </si>
+  <si>
+    <t>📦 Açılmış paketlerin ağzını kapatmaya yardımcı olur.</t>
+  </si>
+  <si>
+    <t>🔄 Tekrar tekrar kullanılabilir.</t>
+  </si>
+  <si>
+    <t>✋ Pratik şekilde takılıp çıkarılabilir.</t>
+  </si>
+  <si>
+    <t>🏠 Mutfak, ofis ve günlük kullanıma uygundur.</t>
+  </si>
+  <si>
+    <t>🎨 Farklı renk ve figür seçenekleri bulunabilir.</t>
+  </si>
+  <si>
+    <t>🇹🇷 Türkiye'de üretilmektedir.</t>
+  </si>
+  <si>
+    <t>Kullanım: Paketin açık kısmını katlayınız ve klipsi katlanan bölüme uygun şekilde yerleştirerek sabitleyiniz.</t>
+  </si>
+  <si>
+    <t>Paket İçeriği: 1 adet 3D Baskı Hayvan Figürlü Poşet Klipsi.</t>
+  </si>
+  <si>
+    <t>Önemli: Satış fiyatı 1 adet ürün içindir. Görsellerde farklı renk ve figürler ürün seçeneklerini göstermek amacıyla birlikte sergilenebilir.</t>
+  </si>
+  <si>
+    <t>Not: Ürün 3D baskı yöntemiyle üretildiğinden yüzeyinde ince katman çizgileri ve küçük dokusal farklılıklar görülebilir. Bu durum 3D baskı üretim yönteminin doğal bir özelliğidir.</t>
   </si>
 </sst>
 </file>
@@ -2644,7 +2731,7 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="30" ht="18.0" customHeight="1">
+    <row r="30">
       <c r="A30" s="1" t="s">
         <v>213</v>
       </c>
@@ -2688,55 +2775,178 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="31" ht="18.0" customHeight="1">
-      <c r="M31" s="20"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="3">
+        <v>59.0</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="16">
+        <v>129.9</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="N31" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R31" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="32" ht="18.0" customHeight="1">
-      <c r="M32" s="20"/>
+      <c r="A32" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" s="17">
+        <v>59.0</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="16">
+        <v>99.9</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="N32" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q32" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R32" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="S32" s="17">
+        <v>1.0</v>
+      </c>
+      <c r="T32" s="17"/>
     </row>
     <row r="33" ht="18.0" customHeight="1">
-      <c r="M33" s="20"/>
+      <c r="M33" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N33" s="1"/>
     </row>
     <row r="34" ht="18.0" customHeight="1">
-      <c r="M34" s="20"/>
+      <c r="M34" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="N34" s="1"/>
     </row>
     <row r="35" ht="18.0" customHeight="1">
-      <c r="M35" s="21"/>
+      <c r="M35" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="N35" s="1"/>
     </row>
     <row r="36" ht="18.0" customHeight="1">
-      <c r="M36" s="20"/>
+      <c r="M36" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="N36" s="1"/>
     </row>
     <row r="37" ht="18.0" customHeight="1">
-      <c r="M37" s="21"/>
+      <c r="M37" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N37" s="1"/>
     </row>
     <row r="38" ht="18.0" customHeight="1">
-      <c r="M38" s="20"/>
+      <c r="M38" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N38" s="1"/>
     </row>
     <row r="39" ht="18.0" customHeight="1">
-      <c r="M39" s="21"/>
+      <c r="M39" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="N39" s="1"/>
     </row>
     <row r="40" ht="18.0" customHeight="1">
-      <c r="M40" s="20"/>
+      <c r="M40" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="N40" s="1"/>
     </row>
     <row r="41" ht="18.0" customHeight="1">
-      <c r="M41" s="21"/>
+      <c r="M41" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="N41" s="1"/>
     </row>
     <row r="42" ht="18.0" customHeight="1">
-      <c r="M42" s="20"/>
+      <c r="M42" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="N42" s="1"/>
     </row>
     <row r="43" ht="18.0" customHeight="1">
-      <c r="M43" s="21"/>
+      <c r="M43" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="N43" s="1"/>
     </row>
     <row r="44" ht="18.0" customHeight="1">
-      <c r="M44" s="20"/>
+      <c r="M44" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="N44" s="1"/>
     </row>
     <row r="45" ht="18.0" customHeight="1">
-      <c r="M45" s="20"/>
+      <c r="M45" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="N45" s="1"/>
     </row>
     <row r="46" ht="18.0" customHeight="1">
-      <c r="M46" s="20"/>
+      <c r="M46" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="N46" s="1"/>
     </row>
     <row r="47" ht="18.0" customHeight="1">
       <c r="M47" s="20"/>
@@ -3737,7 +3947,9 @@
     <hyperlink r:id="rId27" ref="N28"/>
     <hyperlink r:id="rId28" ref="N29"/>
     <hyperlink r:id="rId29" ref="N30"/>
+    <hyperlink r:id="rId30" ref="N31"/>
+    <hyperlink r:id="rId31" ref="N32"/>
   </hyperlinks>
-  <drawing r:id="rId30"/>
+  <drawing r:id="rId32"/>
 </worksheet>
 </file>
--- a/ognami.xlsx
+++ b/ognami.xlsx
@@ -2578,7 +2578,7 @@
     <t>SKU000186</t>
   </si>
   <si>
-    <t>3D Baskı Sevimli Hayvan Figürlü Poşet Klipsi | Paket Kapatma Mandalı | Tekrar Kullanılabilir Gıda Poşeti Klipsi</t>
+    <t>3D Baskı Sevimli Hayvan Figürlü Poşet Klipsi | Paket Kapatma Mandalı</t>
   </si>
   <si>
     <t>Pratik Gereçler</t>

--- a/ognami.xlsx
+++ b/ognami.xlsx
@@ -2357,7 +2357,14 @@
     <t>SKU000165</t>
   </si>
   <si>
-    <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/6487138f-bc14-4f01-b495-347ffc7ef83e/86ea7171-f4fb-4f64-94f3-c94e8f39b63e.png</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>https://cdn.dsmcdn.com/public-spm-prod8/spm-product-image/634668/6487138f-bc14-4f01-b495-347ffc7ef83e/86ea7171-f4fb-4f64-94f3-c94e8f39b63e.png</t>
+    </r>
   </si>
   <si>
     <t>OGN9990000166</t>
@@ -2578,7 +2585,7 @@
     <t>SKU000186</t>
   </si>
   <si>
-    <t>3D Baskı Sevimli Hayvan Figürlü Poşet Klipsi | Paket Kapatma Mandalı</t>
+    <t>3D Baskı Sevimli Hayvan Figürlü Poşet Klipsi | Paket Kapatma Mandalı | Tekrar Kullanılabilir Gıda Poşeti Klipsi</t>
   </si>
   <si>
     <t>Pratik Gereçler</t>
@@ -7160,7 +7167,7 @@
         <v>25</v>
       </c>
       <c r="L85" s="6">
-        <v>395.0</v>
+        <v>345.0</v>
       </c>
       <c r="M85" s="14" t="s">
         <v>342</v>
@@ -7207,7 +7214,7 @@
         <v>25</v>
       </c>
       <c r="L86" s="6">
-        <v>390.0</v>
+        <v>340.0</v>
       </c>
       <c r="M86" s="14" t="s">
         <v>342</v>
@@ -7255,7 +7262,7 @@
         <v>25</v>
       </c>
       <c r="L87" s="6">
-        <v>395.0</v>
+        <v>345.0</v>
       </c>
       <c r="M87" s="14" t="s">
         <v>342</v>
@@ -7301,7 +7308,7 @@
         <v>25</v>
       </c>
       <c r="L88" s="6">
-        <v>395.0</v>
+        <v>345.0</v>
       </c>
       <c r="M88" s="14" t="s">
         <v>342</v>
@@ -7347,7 +7354,7 @@
         <v>25</v>
       </c>
       <c r="L89" s="6">
-        <v>385.0</v>
+        <v>335.0</v>
       </c>
       <c r="M89" s="14" t="s">
         <v>342</v>
@@ -7394,7 +7401,7 @@
         <v>25</v>
       </c>
       <c r="L90" s="6">
-        <v>395.0</v>
+        <v>345.0</v>
       </c>
       <c r="M90" s="14" t="s">
         <v>342</v>
@@ -7440,7 +7447,7 @@
         <v>25</v>
       </c>
       <c r="L91" s="6">
-        <v>399.0</v>
+        <v>345.0</v>
       </c>
       <c r="M91" s="14" t="s">
         <v>342</v>
@@ -7487,7 +7494,7 @@
         <v>25</v>
       </c>
       <c r="L92" s="6">
-        <v>395.0</v>
+        <v>345.0</v>
       </c>
       <c r="M92" s="14" t="s">
         <v>342</v>
@@ -10988,9 +10995,10 @@
       <c r="M166" s="14" t="s">
         <v>632</v>
       </c>
-      <c r="N166" s="12" t="s">
+      <c r="N166" s="7" t="s">
         <v>642</v>
       </c>
+      <c r="O166" s="8"/>
       <c r="P166" s="8"/>
       <c r="Q166" s="3" t="s">
         <v>28</v>
@@ -29317,7 +29325,7 @@
       <c r="S999" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="252">
+  <mergeCells count="251">
     <mergeCell ref="N129:P129"/>
     <mergeCell ref="N131:P131"/>
     <mergeCell ref="N132:O132"/>
@@ -29543,7 +29551,6 @@
     <mergeCell ref="N163:O163"/>
     <mergeCell ref="N164:P164"/>
     <mergeCell ref="N165:P165"/>
-    <mergeCell ref="N166:O166"/>
     <mergeCell ref="N167:O167"/>
     <mergeCell ref="N168:P168"/>
     <mergeCell ref="N169:O169"/>
@@ -29555,21 +29562,21 @@
     <mergeCell ref="N176:P176"/>
     <mergeCell ref="N177:P177"/>
     <mergeCell ref="N178:O178"/>
+    <mergeCell ref="N186:P186"/>
+    <mergeCell ref="N187:O187"/>
+    <mergeCell ref="N188:P188"/>
+    <mergeCell ref="N189:P189"/>
+    <mergeCell ref="N190:P190"/>
+    <mergeCell ref="N191:P191"/>
+    <mergeCell ref="N192:P192"/>
+    <mergeCell ref="N193:P193"/>
     <mergeCell ref="N179:P179"/>
     <mergeCell ref="N180:P180"/>
     <mergeCell ref="N181:P181"/>
     <mergeCell ref="N182:O182"/>
     <mergeCell ref="N183:P183"/>
     <mergeCell ref="N184:O184"/>
-    <mergeCell ref="N192:P192"/>
-    <mergeCell ref="N193:P193"/>
     <mergeCell ref="N185:P185"/>
-    <mergeCell ref="N186:P186"/>
-    <mergeCell ref="N187:O187"/>
-    <mergeCell ref="N188:P188"/>
-    <mergeCell ref="N189:P189"/>
-    <mergeCell ref="N190:P190"/>
-    <mergeCell ref="N191:P191"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="N2"/>
